--- a/tests/dicz/dicz1.xlsx
+++ b/tests/dicz/dicz1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\MyPy\Packages\fltk\tests\dicz\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C38371A6-4347-477F-A4FE-792303D1B683}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBA2F9E9-F7A2-4E62-B5AA-D3A116DEE854}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -784,8 +784,8 @@
         <v>78</v>
       </c>
       <c r="C5" t="b">
-        <f>FALSE()</f>
-        <v>0</v>
+        <f>TRUE()</f>
+        <v>1</v>
       </c>
       <c r="E5" t="s">
         <v>68</v>
@@ -1051,8 +1051,8 @@
         <v>14</v>
       </c>
       <c r="C14" t="b">
-        <f>FALSE()</f>
-        <v>0</v>
+        <f>TRUE()</f>
+        <v>1</v>
       </c>
       <c r="E14" t="s">
         <v>26</v>
